--- a/output/Data and Chart Outputs/us_gas.xlsx
+++ b/output/Data and Chart Outputs/us_gas.xlsx
@@ -28,9 +28,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -70,13 +71,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -367,7 +367,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr/>
           </a:p>
@@ -405,6 +405,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -501,7 +507,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr/>
           </a:p>
@@ -539,6 +545,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -723,7 +735,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr/>
           </a:p>
@@ -761,6 +773,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -790,7 +808,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>US Lower 48 working gas in storage (EIA) - water year (Oct-Sep), data to 2026-09-18</a:t>
+              <a:t>US Lower 48 working gas in storage (EIA) - water year (Oct-Sep), data to 2026-09-25</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -971,23 +989,66 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="4000"/>
+          <min val="1000"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Bcf</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
+        <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <majorUnit val="500"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -1017,7 +1078,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>US East working gas in storage (EIA) - water year (Oct-Sep), data to 2026-09-18</a:t>
+              <a:t>US East working gas in storage (EIA) - water year (Oct-Sep), data to 2026-09-25</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1198,23 +1259,66 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="1000"/>
+          <min val="200"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Bcf</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
+        <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <majorUnit val="200"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -1244,7 +1348,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>US Midwest working gas in storage (EIA) - water year (Oct-Sep), data to 2026-09-18</a:t>
+              <a:t>US Midwest working gas in storage (EIA) - water year (Oct-Sep), data to 2026-09-25</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1425,23 +1529,66 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="1200"/>
+          <min val="200"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Bcf</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
+        <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <majorUnit val="200"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -1471,7 +1618,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>US Mountain working gas in storage (EIA) - water year (Oct-Sep), data to 2026-09-18</a:t>
+              <a:t>US Mountain working gas in storage (EIA) - water year (Oct-Sep), data to 2026-09-25</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1652,23 +1799,66 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="300"/>
+          <min val="50"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Bcf</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
+        <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <majorUnit val="50"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -1698,7 +1888,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>US Pacific working gas in storage (EIA) - water year (Oct-Sep), data to 2026-09-18</a:t>
+              <a:t>US Pacific working gas in storage (EIA) - water year (Oct-Sep), data to 2026-09-25</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1879,23 +2069,66 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="350"/>
+          <min val="50"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Bcf</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
+        <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <majorUnit val="50"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -1925,7 +2158,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>US South Central working gas in storage (EIA) - water year (Oct-Sep), data to 2026-09-18</a:t>
+              <a:t>US South Central working gas in storage (EIA) - water year (Oct-Sep), data to 2026-09-25</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2106,23 +2339,66 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="1400"/>
+          <min val="400"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Bcf</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
+        <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <majorUnit val="200"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -2713,6 +2989,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -2727,6 +3004,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -11719,6 +11997,9 @@
       <c r="F355" t="n">
         <v>1190</v>
       </c>
+      <c r="G355" t="n">
+        <v>1042</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -11741,6 +12022,9 @@
       <c r="F356" t="n">
         <v>1189.43</v>
       </c>
+      <c r="G356" t="n">
+        <v>1043</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -11763,6 +12047,9 @@
       <c r="F357" t="n">
         <v>1188.86</v>
       </c>
+      <c r="G357" t="n">
+        <v>1044</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -11785,6 +12072,9 @@
       <c r="F358" t="n">
         <v>1188.29</v>
       </c>
+      <c r="G358" t="n">
+        <v>1045</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -11807,6 +12097,9 @@
       <c r="F359" t="n">
         <v>1187.71</v>
       </c>
+      <c r="G359" t="n">
+        <v>1046</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -11829,6 +12122,9 @@
       <c r="F360" t="n">
         <v>1187.14</v>
       </c>
+      <c r="G360" t="n">
+        <v>1047</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -11850,6 +12146,9 @@
       </c>
       <c r="F361" t="n">
         <v>1186.57</v>
+      </c>
+      <c r="G361" t="n">
+        <v>1048</v>
       </c>
     </row>
     <row r="362">
@@ -20714,7 +21013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G613"/>
+  <dimension ref="A1:G614"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34828,6 +35127,29 @@
       </c>
       <c r="G613" t="n">
         <v>292</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="4" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B614" t="n">
+        <v>3415</v>
+      </c>
+      <c r="C614" t="n">
+        <v>840</v>
+      </c>
+      <c r="D614" t="n">
+        <v>984</v>
+      </c>
+      <c r="E614" t="n">
+        <v>1048</v>
+      </c>
+      <c r="F614" t="n">
+        <v>248</v>
+      </c>
+      <c r="G614" t="n">
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -34885,7 +35207,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -34908,7 +35230,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -34931,7 +35253,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -34954,7 +35276,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -34977,7 +35299,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -35000,7 +35322,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -35023,7 +35345,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -35046,7 +35368,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -35069,7 +35391,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -35092,7 +35414,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -35115,7 +35437,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -35138,7 +35460,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -35161,7 +35483,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -35184,7 +35506,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -35207,7 +35529,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -35230,7 +35552,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -35253,7 +35575,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -35276,7 +35598,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -35299,7 +35621,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -35322,7 +35644,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -35345,7 +35667,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -35368,7 +35690,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -35391,7 +35713,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -35414,7 +35736,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -35437,7 +35759,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -35460,7 +35782,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -35483,7 +35805,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -35506,7 +35828,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -35529,7 +35851,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -35552,7 +35874,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -35575,7 +35897,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -35598,7 +35920,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -35621,7 +35943,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -35644,7 +35966,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -35667,7 +35989,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -35690,7 +36012,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -35713,7 +36035,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -35736,7 +36058,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -35759,7 +36081,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -35782,7 +36104,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -35805,7 +36127,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -35828,7 +36150,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -35851,7 +36173,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -35874,7 +36196,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -35897,7 +36219,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -35920,7 +36242,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -35943,7 +36265,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -35966,7 +36288,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -35989,7 +36311,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -36012,7 +36334,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -36035,7 +36357,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -36058,7 +36380,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -36081,7 +36403,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -36104,7 +36426,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -36127,7 +36449,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -36150,7 +36472,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -36173,7 +36495,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -36196,7 +36518,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -36219,7 +36541,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -36242,7 +36564,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -36265,7 +36587,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -36288,7 +36610,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -36311,7 +36633,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -36334,7 +36656,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -36357,7 +36679,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -36380,7 +36702,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -36403,7 +36725,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -36456,7 +36778,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -36464,7 +36786,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -36472,7 +36794,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -36480,7 +36802,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -36488,7 +36810,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -36496,7 +36818,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -36504,7 +36826,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -36512,7 +36834,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -36520,7 +36842,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -36528,7 +36850,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -36536,7 +36858,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -36544,7 +36866,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -36552,7 +36874,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -36560,7 +36882,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -36568,7 +36890,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -36576,7 +36898,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -36584,7 +36906,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -36592,7 +36914,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -36600,7 +36922,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -36608,7 +36930,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -36616,7 +36938,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -36624,7 +36946,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -36632,7 +36954,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -36640,7 +36962,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -36648,7 +36970,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -36656,7 +36978,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -36664,7 +36986,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -36672,7 +36994,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -36680,7 +37002,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -36688,7 +37010,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -36696,7 +37018,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -36704,7 +37026,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -36712,7 +37034,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -36720,7 +37042,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -36728,7 +37050,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -36736,7 +37058,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -36744,7 +37066,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -36752,7 +37074,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -36760,7 +37082,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -36768,7 +37090,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -36776,7 +37098,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -36784,7 +37106,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -36792,7 +37114,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -36800,7 +37122,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -36808,7 +37130,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -36816,7 +37138,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -36824,7 +37146,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -36832,7 +37154,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -36840,7 +37162,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -36848,7 +37170,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -36856,7 +37178,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -36864,7 +37186,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -36872,7 +37194,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -36880,7 +37202,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -36888,7 +37210,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -36896,7 +37218,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -36904,7 +37226,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -36912,7 +37234,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -36920,7 +37242,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -36928,7 +37250,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -36936,7 +37258,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -36944,7 +37266,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -36952,7 +37274,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -36960,7 +37282,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -36968,7 +37290,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -36976,7 +37298,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -36984,7 +37306,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -37037,7 +37359,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -37054,7 +37376,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -37071,7 +37393,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -37088,7 +37410,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -37105,7 +37427,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -37122,7 +37444,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -37139,7 +37461,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -37156,7 +37478,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -37173,7 +37495,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -37190,7 +37512,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -37207,7 +37529,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -37224,7 +37546,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -37241,7 +37563,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -37258,7 +37580,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -37275,7 +37597,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -37292,7 +37614,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -37309,7 +37631,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -37326,7 +37648,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -37343,7 +37665,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -37360,7 +37682,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -37377,7 +37699,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -37394,7 +37716,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -37411,7 +37733,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -37428,7 +37750,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -37445,7 +37767,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -37462,7 +37784,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -37479,7 +37801,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -37496,7 +37818,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -37513,7 +37835,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -37530,7 +37852,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -37547,7 +37869,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -37564,7 +37886,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -37581,7 +37903,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -37598,7 +37920,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -37615,7 +37937,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -37632,7 +37954,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -37649,7 +37971,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -37666,7 +37988,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -37683,7 +38005,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -37700,7 +38022,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -37717,7 +38039,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -37734,7 +38056,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -37751,7 +38073,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -37768,7 +38090,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -37785,7 +38107,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -37802,7 +38124,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -37819,7 +38141,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -37836,7 +38158,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -37853,7 +38175,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -37870,7 +38192,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -37887,7 +38209,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -37904,7 +38226,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -37921,7 +38243,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -37938,7 +38260,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -37955,7 +38277,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -37972,7 +38294,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -37989,7 +38311,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -38006,7 +38328,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -38023,7 +38345,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -38040,7 +38362,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -38057,7 +38379,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -38074,7 +38396,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -38091,7 +38413,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -38108,7 +38430,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -38125,7 +38447,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -38142,7 +38464,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -38159,7 +38481,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -47147,6 +47469,9 @@
       <c r="F355" t="n">
         <v>3499</v>
       </c>
+      <c r="G355" t="n">
+        <v>3360.14</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -47169,6 +47494,9 @@
       <c r="F356" t="n">
         <v>3506.43</v>
       </c>
+      <c r="G356" t="n">
+        <v>3369.29</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -47191,6 +47519,9 @@
       <c r="F357" t="n">
         <v>3513.86</v>
       </c>
+      <c r="G357" t="n">
+        <v>3378.43</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -47213,6 +47544,9 @@
       <c r="F358" t="n">
         <v>3521.29</v>
       </c>
+      <c r="G358" t="n">
+        <v>3387.57</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -47235,6 +47569,9 @@
       <c r="F359" t="n">
         <v>3528.71</v>
       </c>
+      <c r="G359" t="n">
+        <v>3396.71</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -47257,6 +47594,9 @@
       <c r="F360" t="n">
         <v>3536.14</v>
       </c>
+      <c r="G360" t="n">
+        <v>3405.86</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -47278,6 +47618,9 @@
       </c>
       <c r="F361" t="n">
         <v>3543.57</v>
+      </c>
+      <c r="G361" t="n">
+        <v>3415</v>
       </c>
     </row>
     <row r="362">
@@ -56362,6 +56705,9 @@
       <c r="F355" t="n">
         <v>807</v>
       </c>
+      <c r="G355" t="n">
+        <v>818.5700000000001</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -56384,6 +56730,9 @@
       <c r="F356" t="n">
         <v>810.5700000000001</v>
       </c>
+      <c r="G356" t="n">
+        <v>822.14</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -56406,6 +56755,9 @@
       <c r="F357" t="n">
         <v>814.14</v>
       </c>
+      <c r="G357" t="n">
+        <v>825.71</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -56428,6 +56780,9 @@
       <c r="F358" t="n">
         <v>817.71</v>
       </c>
+      <c r="G358" t="n">
+        <v>829.29</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -56450,6 +56805,9 @@
       <c r="F359" t="n">
         <v>821.29</v>
       </c>
+      <c r="G359" t="n">
+        <v>832.86</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -56472,6 +56830,9 @@
       <c r="F360" t="n">
         <v>824.86</v>
       </c>
+      <c r="G360" t="n">
+        <v>836.4299999999999</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -56493,6 +56854,9 @@
       </c>
       <c r="F361" t="n">
         <v>828.4299999999999</v>
+      </c>
+      <c r="G361" t="n">
+        <v>840</v>
       </c>
     </row>
     <row r="362">
@@ -65577,6 +65941,9 @@
       <c r="F355" t="n">
         <v>945</v>
       </c>
+      <c r="G355" t="n">
+        <v>962.5700000000001</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -65599,6 +65966,9 @@
       <c r="F356" t="n">
         <v>948.86</v>
       </c>
+      <c r="G356" t="n">
+        <v>966.14</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -65621,6 +65991,9 @@
       <c r="F357" t="n">
         <v>952.71</v>
       </c>
+      <c r="G357" t="n">
+        <v>969.71</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -65643,6 +66016,9 @@
       <c r="F358" t="n">
         <v>956.5700000000001</v>
       </c>
+      <c r="G358" t="n">
+        <v>973.29</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -65665,6 +66041,9 @@
       <c r="F359" t="n">
         <v>960.4299999999999</v>
       </c>
+      <c r="G359" t="n">
+        <v>976.86</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -65687,6 +66066,9 @@
       <c r="F360" t="n">
         <v>964.29</v>
       </c>
+      <c r="G360" t="n">
+        <v>980.4299999999999</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -65708,6 +66090,9 @@
       </c>
       <c r="F361" t="n">
         <v>968.14</v>
+      </c>
+      <c r="G361" t="n">
+        <v>984</v>
       </c>
     </row>
     <row r="362">
@@ -74792,6 +75177,9 @@
       <c r="F355" t="n">
         <v>256</v>
       </c>
+      <c r="G355" t="n">
+        <v>244.57</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -74814,6 +75202,9 @@
       <c r="F356" t="n">
         <v>256.43</v>
       </c>
+      <c r="G356" t="n">
+        <v>245.14</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -74836,6 +75227,9 @@
       <c r="F357" t="n">
         <v>256.86</v>
       </c>
+      <c r="G357" t="n">
+        <v>245.71</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -74858,6 +75252,9 @@
       <c r="F358" t="n">
         <v>257.29</v>
       </c>
+      <c r="G358" t="n">
+        <v>246.29</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -74880,6 +75277,9 @@
       <c r="F359" t="n">
         <v>257.71</v>
       </c>
+      <c r="G359" t="n">
+        <v>246.86</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -74902,6 +75302,9 @@
       <c r="F360" t="n">
         <v>258.14</v>
       </c>
+      <c r="G360" t="n">
+        <v>247.43</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -74923,6 +75326,9 @@
       </c>
       <c r="F361" t="n">
         <v>258.57</v>
+      </c>
+      <c r="G361" t="n">
+        <v>248</v>
       </c>
     </row>
     <row r="362">
@@ -84007,6 +84413,9 @@
       <c r="F355" t="n">
         <v>300</v>
       </c>
+      <c r="G355" t="n">
+        <v>292.43</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -84029,6 +84438,9 @@
       <c r="F356" t="n">
         <v>300.29</v>
       </c>
+      <c r="G356" t="n">
+        <v>292.86</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -84051,6 +84463,9 @@
       <c r="F357" t="n">
         <v>300.57</v>
       </c>
+      <c r="G357" t="n">
+        <v>293.29</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -84073,6 +84488,9 @@
       <c r="F358" t="n">
         <v>300.86</v>
       </c>
+      <c r="G358" t="n">
+        <v>293.71</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -84095,6 +84513,9 @@
       <c r="F359" t="n">
         <v>301.14</v>
       </c>
+      <c r="G359" t="n">
+        <v>294.14</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -84117,6 +84538,9 @@
       <c r="F360" t="n">
         <v>301.43</v>
       </c>
+      <c r="G360" t="n">
+        <v>294.57</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -84138,6 +84562,9 @@
       </c>
       <c r="F361" t="n">
         <v>301.71</v>
+      </c>
+      <c r="G361" t="n">
+        <v>295</v>
       </c>
     </row>
     <row r="362">
